--- a/etf_holdings/2026-10-25_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-25_00405A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-25 21:17:10</t>
+          <t>2026-10-25 21:22:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1393,6 +1393,1836 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2059川湖</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-3.22%9755</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.22%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>9755</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.26%50,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-5.33%1420</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.33%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.01%306,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>306000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2330台積電</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-1.45%2385</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2385</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.98%179,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>179000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-6.02%1560</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.02%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.44%200,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6187萬潤</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-5.26%1260</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.26%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.86%148,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-2.13%1840</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1840</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.84%99,139</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>99139</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-4%1560</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.68%94,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>94000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6526達發</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-3.47%778</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-3.47%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>778</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.53%146,000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>146000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>6515穎崴</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-3.52%4795</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-3.52%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>4795</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.51%23,000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3189景碩</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-2.38%986</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-2.38%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>986</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.23%50,000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-3.3%161</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-3.3%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>161</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.16%211,000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>211000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>6285啟碁</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-6.69%230</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-6.69%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>230</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.11%100,000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-5.58%262.5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.58%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.05%42,650</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>42650</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3264欣銓</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-6.98%246.5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-6.98%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.04%34,000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:22:59</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>+0.08%6175</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>6175</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.03%1,000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>8021尖點</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-5.34%479</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5.34%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>479</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.02%10,217</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>10217</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-1.95%125.5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.02%28,000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3661世芯-KY</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-5.8%3495</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5.8%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>3495</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.02%1,000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2395研華</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-1.9%670</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>670</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.02%5,000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6510精測</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-5.11%3065</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.11%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>3065</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>6278台表科</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-8.21%290.5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-8.21%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.01%10,000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6446藥華藥</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-1.28%1160</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.01%2,000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3450聯鈞</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-5.78%424</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5.78%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>424</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>&lt;0.01%5,000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-4.39%654</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-4.39%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>654</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>&lt;0.01%3,000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3533嘉澤</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-1.37%1795</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1795</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3605宏致</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-3.65%171.5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-3.65%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>&lt;0.01%10,000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1303南亞</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-6.08%301</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-6.08%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>301</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>&lt;0.01%5,000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3491昇達科</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-7.69%1320</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-7.69%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1590亞德客-KY</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-1.79%1100</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-1.79%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:23:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8150南茂</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-6.44%95.9</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-6.44%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>&lt;0.01%10,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-25_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-25_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:57</t>
+          <t>2026-10-25 21:44:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:59</t>
+          <t>2026-10-25 21:44:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-25 21:23:00</t>
+          <t>2026-10-25 21:44:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
